--- a/images/___images_sizing.xlsx
+++ b/images/___images_sizing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richtap/git/slovenskivedci/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5FD250-E0B5-FA4E-A2F5-270FA7C36E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AAE65C-AAF7-7244-A54E-71C3B6AF47A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7820" yWindow="1760" windowWidth="26740" windowHeight="15500" xr2:uid="{FBABA11E-B330-2F49-B6C1-0584A0817DCB}"/>
   </bookViews>
@@ -121,9 +121,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -161,7 +161,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -267,7 +267,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,7 +409,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -434,11 +434,11 @@
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>400</v>
+        <v>512</v>
       </c>
       <c r="B3" s="3">
         <f>A3/1.78</f>
-        <v>224.71910112359549</v>
+        <v>287.64044943820227</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>

--- a/images/___images_sizing.xlsx
+++ b/images/___images_sizing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richtap/git/slovenskivedci/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AAE65C-AAF7-7244-A54E-71C3B6AF47A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E966DCD-52D3-2745-A2BF-C0D6B40C53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7820" yWindow="1760" windowWidth="26740" windowHeight="15500" xr2:uid="{FBABA11E-B330-2F49-B6C1-0584A0817DCB}"/>
   </bookViews>
@@ -434,11 +434,11 @@
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>512</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3">
         <f>A3/1.78</f>
-        <v>287.64044943820227</v>
+        <v>224.71910112359549</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>

--- a/images/___images_sizing.xlsx
+++ b/images/___images_sizing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richtap/git/slovenskivedci/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E966DCD-52D3-2745-A2BF-C0D6B40C53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F0F5D7-508E-2A45-AC48-DD1D98DA4723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7820" yWindow="1760" windowWidth="26740" windowHeight="15500" xr2:uid="{FBABA11E-B330-2F49-B6C1-0584A0817DCB}"/>
   </bookViews>
@@ -434,11 +434,11 @@
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>400</v>
+        <v>225</v>
       </c>
       <c r="B3" s="3">
         <f>A3/1.78</f>
-        <v>224.71910112359549</v>
+        <v>126.40449438202246</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>

--- a/images/___images_sizing.xlsx
+++ b/images/___images_sizing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richtap/git/slovenskivedci/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F0F5D7-508E-2A45-AC48-DD1D98DA4723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D1AC30-A325-A54F-986E-846F5C0775F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7820" yWindow="1760" windowWidth="26740" windowHeight="15500" xr2:uid="{FBABA11E-B330-2F49-B6C1-0584A0817DCB}"/>
   </bookViews>
@@ -434,11 +434,11 @@
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>225</v>
+        <v>679</v>
       </c>
       <c r="B3" s="3">
         <f>A3/1.78</f>
-        <v>126.40449438202246</v>
+        <v>381.46067415730334</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>

--- a/images/___images_sizing.xlsx
+++ b/images/___images_sizing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richtap/git/slovenskivedci/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D1AC30-A325-A54F-986E-846F5C0775F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ED7A1E-360E-7B4A-90BE-AF043B7E7758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7820" yWindow="1760" windowWidth="26740" windowHeight="15500" xr2:uid="{FBABA11E-B330-2F49-B6C1-0584A0817DCB}"/>
   </bookViews>
@@ -434,11 +434,11 @@
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>679</v>
+        <v>959</v>
       </c>
       <c r="B3" s="3">
         <f>A3/1.78</f>
-        <v>381.46067415730334</v>
+        <v>538.76404494382018</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>

--- a/images/___images_sizing.xlsx
+++ b/images/___images_sizing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/richtap/git/slovenskivedci/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39ED7A1E-360E-7B4A-90BE-AF043B7E7758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0CB94A-3BE0-5A43-8C5F-288D08A5B4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7820" yWindow="1760" windowWidth="26740" windowHeight="15500" xr2:uid="{FBABA11E-B330-2F49-B6C1-0584A0817DCB}"/>
   </bookViews>
@@ -434,11 +434,11 @@
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>959</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3">
         <f>A3/1.78</f>
-        <v>538.76404494382018</v>
+        <v>224.71910112359549</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>
